--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-fonctions-physiques.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-fonctions-physiques.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3207" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3221" uniqueCount="349">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -484,6 +484,9 @@
 </t>
   </si>
   <si>
+    <t>Can serve as a target of a linkHtml reference</t>
+  </si>
+  <si>
     <t>Section.classCode</t>
   </si>
   <si>
@@ -673,6 +676,9 @@
     <t>Titre de la section</t>
   </si>
   <si>
+    <t>If valued, it is to be rendered as part of the narrative content of the clinical document body.</t>
+  </si>
+  <si>
     <t>Section.text</t>
   </si>
   <si>
@@ -683,10 +689,25 @@
     <t>Bloc narratif</t>
   </si>
   <si>
+    <t>Also referred to as the CDA Narrative Block</t>
+  </si>
+  <si>
     <t>Section.confidentialityCode</t>
   </si>
   <si>
+    <t>Controls the disclosure of information in this section</t>
+  </si>
+  <si>
+    <t>A value for Section.confidentialityCode overrides the value propagated from StructuredBody.</t>
+  </si>
+  <si>
     <t>Section.languageCode</t>
+  </si>
+  <si>
+    <t>Human language of character data</t>
+  </si>
+  <si>
+    <t>A value for Section.languageCode overrides the value propagated from StructuredBody.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/all-languages</t>
@@ -699,6 +720,15 @@
 </t>
   </si>
   <si>
+    <t>Primary target of the entries recorded in a section</t>
+  </si>
+  <si>
+    <t>Most of the time the subject is the same as the recordTarget, but need not be, for instance when the subject is a fetus observed in an obstetrical ultrasound.</t>
+  </si>
+  <si>
+    <t>The subject participant can be ascribed to a CDA section or a CDA entry. It propagates to nested components, unless overridden. The subject of a document is presumed to be the patient.</t>
+  </si>
+  <si>
     <t>Section.author</t>
   </si>
   <si>
@@ -706,6 +736,9 @@
 </t>
   </si>
   <si>
+    <t>The author participant can be ascribed to a CDA section, where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.informant</t>
   </si>
   <si>
@@ -713,6 +746,9 @@
 </t>
   </si>
   <si>
+    <t>The informant participant can be ascribed to a CDA section where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.entry</t>
   </si>
   <si>
@@ -1013,6 +1049,12 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/InfrastructureRoot
 </t>
+  </si>
+  <si>
+    <t>Used to nest a Section within a Section</t>
+  </si>
+  <si>
+    <t>Context propagates to nested sections</t>
   </si>
   <si>
     <t>Section.component.nullFlavor</t>
@@ -1389,7 +1431,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="148.87109375" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -3810,7 +3852,9 @@
       <c r="K24" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="L24" s="2"/>
+      <c r="L24" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3881,10 +3925,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3918,7 +3962,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>74</v>
@@ -3940,7 +3984,7 @@
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>74</v>
@@ -3958,7 +4002,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3978,10 +4022,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4015,7 +4059,7 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>74</v>
@@ -4037,7 +4081,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>74</v>
@@ -4055,7 +4099,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4075,10 +4119,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4092,7 +4136,7 @@
         <v>75</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>74</v>
@@ -4104,10 +4148,10 @@
         <v>95</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4158,7 +4202,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4178,10 +4222,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4195,7 +4239,7 @@
         <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>74</v>
@@ -4204,13 +4248,13 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4261,7 +4305,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4281,10 +4325,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4382,10 +4426,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4401,7 +4445,7 @@
         <v>75</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>74</v>
@@ -4414,7 +4458,7 @@
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4426,7 +4470,7 @@
         <v>74</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>74</v>
@@ -4465,7 +4509,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4485,17 +4529,17 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>75</v>
@@ -4504,7 +4548,7 @@
         <v>75</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>74</v>
@@ -4517,7 +4561,7 @@
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4529,7 +4573,7 @@
         <v>74</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>74</v>
@@ -4568,7 +4612,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4588,17 +4632,17 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>80</v>
@@ -4620,7 +4664,7 @@
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4632,7 +4676,7 @@
         <v>74</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>74</v>
@@ -4671,7 +4715,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4691,17 +4735,17 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>80</v>
@@ -4723,7 +4767,7 @@
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4774,7 +4818,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4794,17 +4838,17 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>75</v>
@@ -4813,7 +4857,7 @@
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>
@@ -4826,7 +4870,7 @@
       </c>
       <c r="L34" s="2"/>
       <c r="M34" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4838,7 +4882,7 @@
         <v>74</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>74</v>
@@ -4877,7 +4921,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4897,10 +4941,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4923,11 +4967,11 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4978,7 +5022,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4998,10 +5042,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5028,7 +5072,7 @@
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5079,7 +5123,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5099,17 +5143,17 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>80</v>
@@ -5127,11 +5171,11 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5182,7 +5226,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5202,17 +5246,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
@@ -5230,11 +5274,11 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5285,7 +5329,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5305,17 +5349,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
@@ -5333,11 +5377,11 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5388,7 +5432,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5408,10 +5452,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5425,7 +5469,7 @@
         <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -5434,16 +5478,18 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>74</v>
       </c>
@@ -5491,7 +5537,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5511,10 +5557,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5528,7 +5574,7 @@
         <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>
@@ -5537,15 +5583,17 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>74</v>
@@ -5594,7 +5642,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5614,10 +5662,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5640,12 +5688,16 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="L42" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>74</v>
       </c>
@@ -5693,7 +5745,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5713,10 +5765,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5741,10 +5793,14 @@
       <c r="K43" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L43" s="2"/>
+      <c r="L43" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>74</v>
       </c>
@@ -5772,7 +5828,7 @@
       </c>
       <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>74</v>
@@ -5790,7 +5846,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5810,10 +5866,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5836,12 +5892,18 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="L44" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="M44" s="2"/>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+      <c r="N44" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>74</v>
       </c>
@@ -5889,7 +5951,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5909,10 +5971,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5935,12 +5997,14 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>74</v>
       </c>
@@ -5988,7 +6052,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6008,10 +6072,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6034,12 +6098,14 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>74</v>
       </c>
@@ -6087,7 +6153,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6107,10 +6173,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6124,7 +6190,7 @@
         <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>
@@ -6133,7 +6199,7 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
@@ -6174,7 +6240,7 @@
         <v>74</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="AC47" s="2"/>
       <c r="AD47" t="s" s="2">
@@ -6184,7 +6250,7 @@
         <v>124</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6204,13 +6270,13 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>74</v>
@@ -6232,7 +6298,7 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
@@ -6285,7 +6351,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6305,10 +6371,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6406,10 +6472,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6507,10 +6573,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6608,10 +6674,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6709,10 +6775,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6812,10 +6878,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6915,10 +6981,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7018,10 +7084,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7121,10 +7187,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7222,10 +7288,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7255,7 +7321,7 @@
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
@@ -7281,7 +7347,7 @@
       </c>
       <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>74</v>
@@ -7299,7 +7365,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7319,10 +7385,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7356,7 +7422,7 @@
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>74</v>
@@ -7398,7 +7464,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7418,10 +7484,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7444,7 +7510,7 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7497,7 +7563,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7517,10 +7583,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7543,7 +7609,7 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
@@ -7596,7 +7662,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7616,10 +7682,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7642,7 +7708,7 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
@@ -7695,7 +7761,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -7715,10 +7781,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7741,7 +7807,7 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
@@ -7794,7 +7860,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -7814,10 +7880,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7840,10 +7906,10 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
@@ -7895,7 +7961,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -7915,10 +7981,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7941,7 +8007,7 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
@@ -7994,7 +8060,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8014,10 +8080,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8040,7 +8106,7 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -8093,7 +8159,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8113,10 +8179,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8139,7 +8205,7 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -8192,7 +8258,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8212,10 +8278,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8238,7 +8304,7 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -8291,7 +8357,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8311,13 +8377,13 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>74</v>
@@ -8339,7 +8405,7 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -8392,7 +8458,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8412,10 +8478,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8513,10 +8579,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8614,10 +8680,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8715,10 +8781,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8816,10 +8882,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8919,10 +8985,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9022,10 +9088,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9125,10 +9191,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9228,10 +9294,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9329,10 +9395,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9362,7 +9428,7 @@
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
@@ -9388,7 +9454,7 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>74</v>
@@ -9406,7 +9472,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9426,10 +9492,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9463,7 +9529,7 @@
       </c>
       <c r="Q80" s="2"/>
       <c r="R80" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="S80" t="s" s="2">
         <v>74</v>
@@ -9505,7 +9571,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9525,10 +9591,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9551,7 +9617,7 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
@@ -9604,7 +9670,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9624,10 +9690,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9650,7 +9716,7 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -9703,7 +9769,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -9723,10 +9789,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9749,10 +9815,10 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
@@ -9804,7 +9870,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -9824,10 +9890,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9850,7 +9916,7 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
@@ -9903,7 +9969,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -9923,10 +9989,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -9949,7 +10015,7 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -10002,7 +10068,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10022,10 +10088,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10048,7 +10114,7 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -10101,7 +10167,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10121,10 +10187,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10147,7 +10213,7 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -10200,7 +10266,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10220,10 +10286,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10246,7 +10312,7 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -10299,7 +10365,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10319,10 +10385,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10345,7 +10411,7 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -10398,7 +10464,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10418,10 +10484,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10444,12 +10510,16 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="L90" s="2"/>
+        <v>332</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
+      <c r="O90" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>74</v>
       </c>
@@ -10497,7 +10567,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10517,10 +10587,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10618,10 +10688,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10719,10 +10789,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10820,10 +10890,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10921,10 +10991,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11024,10 +11094,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11127,10 +11197,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11230,10 +11300,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11333,10 +11403,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11434,10 +11504,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11464,7 +11534,7 @@
       </c>
       <c r="L100" s="2"/>
       <c r="M100" t="s" s="2">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -11473,7 +11543,7 @@
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>74</v>
@@ -11515,7 +11585,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -11535,10 +11605,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11572,7 +11642,7 @@
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>74</v>
@@ -11614,7 +11684,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -11634,10 +11704,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11660,7 +11730,7 @@
         <v>74</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
@@ -11713,7 +11783,7 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>75</v>
